--- a/TestCases/Timestamp.xlsx
+++ b/TestCases/Timestamp.xlsx
@@ -19,7 +19,7 @@
     <t>time</t>
   </si>
   <si>
-    <t>07:24:55.349964</t>
+    <t>18:02:58.435141</t>
   </si>
 </sst>
 </file>

--- a/TestCases/Timestamp.xlsx
+++ b/TestCases/Timestamp.xlsx
@@ -19,7 +19,7 @@
     <t>time</t>
   </si>
   <si>
-    <t>18:02:58.435141</t>
+    <t>08:22:42.214328</t>
   </si>
 </sst>
 </file>
